--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.144.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.144.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.144" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.144" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,19 +581,15 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.144.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.144.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0144.txt</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>L63: possible duplicated/overlap line with previous line (similarity 68%) :: possession of the said premises ever since (or, and remain-</t>
-        </is>
-      </c>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0144.txt</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" s="1" t="inlineStr"/>
@@ -770,7 +766,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -867,12 +863,12 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.144.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.144.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.144" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.144" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,16 +422,16 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -595,18 +595,18 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: (Pray subpa Ã¦ na.)</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: f the will â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]A</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]A</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: 137</t>
@@ -614,19 +614,19 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L5: isolated marker/symbol line :: 137</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]A</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --------day of ------â€” your orator entered into an the vendor,</t>
+          <t>L45: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --------day of ------— your orator entered into an the vendor,</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --------day of ------â€” your orator entered into an the vendor,</t>
+          <t>L45: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --------day of ------— your orator entered into an the vendor,</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -662,14 +662,10 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: (And for further relief; pray subpa Ã¦ na.)</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: Ã¨removed and applied to his own use aforesaid, and that</t>
+          <t>L10: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: f the will •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -681,7 +677,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: :</t>
+          <t>L5: isolated marker/symbol line :: 137</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -693,7 +689,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L103: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----and</t>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • doned the same and departed this Province, and has re-</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -728,7 +724,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L36: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: (Pray subpÅ“na.) rÃ©.</t>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • doned the same and departed this Province, and has re-</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -740,17 +736,21 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L92: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” concession of the township of â€”- ----in the</t>
+          <t>L49: punctuation artifact: double/multiple hyphen :: — concession of the township of —- ----in the</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L103: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----and</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -766,12 +766,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -781,11 +781,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --------day of ------â€” your orator entered into an the vendor,</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -793,11 +789,15 @@
           <t>L21: isolated marker/symbol line :: K</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L94: isolated marker/symbol line :: —</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L50: punctuation artifact: double/multiple hyphen :: county of ------at or for the price or sum of Â£-</t>
+          <t>L50: punctuation artifact: double/multiple hyphen :: county of ------at or for the price or sum of £-</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
@@ -832,11 +832,7 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” concession of the township of â€”- ----in the</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -848,7 +844,7 @@
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L52: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” payable by ---------equal annual instalments with</t>
+          <t>L52: punctuation artifact: double/multiple hyphen :: — payable by ---------equal annual instalments with</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -883,11 +879,7 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L52: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” payable by ---------equal annual instalments with</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -899,7 +891,7 @@
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: Â£â€” which he paid on the â€” --------day of ------</t>
+          <t>L69: punctuation artifact: double/multiple hyphen :: £— which he paid on the — --------day of ------</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
@@ -934,11 +926,7 @@
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ doned the same and departed this Province, and has re-</t>
-        </is>
-      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -950,7 +938,7 @@
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: the -----â€” day of -------your orator entered into vendee.</t>
+          <t>L90: punctuation artifact: double/multiple hyphen :: the -----— day of -------your orator entered into vendee.</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -985,11 +973,7 @@
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
       <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: Â£â€” which he paid on the â€” --------day of ------</t>
-        </is>
-      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1021,12 +1005,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1036,11 +1020,7 @@
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: the -----â€” day of -------your orator entered into vendee.</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr"/>
@@ -1069,7 +1049,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1079,11 +1059,7 @@
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
       <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
-        </is>
-      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr"/>
@@ -1112,7 +1088,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1190,7 +1166,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
